--- a/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_04_workbook.xlsx
+++ b/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_04_workbook.xlsx
@@ -781,16 +781,16 @@
         <v>800</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03513487428426743</v>
+        <v>0.03141364455223083</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01375</v>
+        <v>0.01125</v>
       </c>
       <c r="E2" t="n">
-        <v>11.09173455315626</v>
+        <v>10.99175596734712</v>
       </c>
       <c r="F2" t="n">
-        <v>4.292897913208891</v>
+        <v>4.115922117927483</v>
       </c>
     </row>
     <row r="3">
@@ -803,16 +803,16 @@
         <v>800</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06491637229919434</v>
+        <v>0.05952248722314835</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0175</v>
+        <v>0.015</v>
       </c>
       <c r="E3" t="n">
-        <v>10.33412801163104</v>
+        <v>10.10747353720687</v>
       </c>
       <c r="F3" t="n">
-        <v>4.001259353863206</v>
+        <v>4.223474187661517</v>
       </c>
     </row>
     <row r="4">
@@ -825,16 +825,16 @@
         <v>800</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09602290391921997</v>
+        <v>0.09011267870664597</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02625</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>9.317424338677371</v>
+        <v>9.313061198565103</v>
       </c>
       <c r="F4" t="n">
-        <v>3.985553088842893</v>
+        <v>3.984369390276518</v>
       </c>
     </row>
     <row r="5">
@@ -847,16 +847,16 @@
         <v>800</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1487506031990051</v>
+        <v>0.1452340334653854</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03375</v>
+        <v>0.045</v>
       </c>
       <c r="E5" t="n">
-        <v>8.717722428102496</v>
+        <v>8.833198336822516</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9542431662731</v>
+        <v>3.862256926772992</v>
       </c>
     </row>
     <row r="6">
@@ -869,16 +869,16 @@
         <v>800</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4899794161319733</v>
+        <v>0.504355251789093</v>
       </c>
       <c r="D6" t="n">
         <v>0.76125</v>
       </c>
       <c r="E6" t="n">
-        <v>9.483256132500918</v>
+        <v>9.698776424126471</v>
       </c>
       <c r="F6" t="n">
-        <v>4.065503195614356</v>
+        <v>4.113434095163938</v>
       </c>
     </row>
   </sheetData>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Cramer's V=0.0737 between REPAYMENT_TIER and Notebook 01's PD-risk band (chi2=87.01, p=8.85e-12); r(capacity ratio, PD)=-0.0071.</t>
+          <t>Cramer's V=0.0678 between REPAYMENT_TIER and Notebook 01's PD-risk band (chi2=73.49, p=2.426e-09); r(capacity ratio, PD)=-0.0022.</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
